--- a/stories/arbres/ATOM-REL.MOQ.002-04.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.002-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Pauline est dans la cour. Maman l'a accompagnée jusqu'au portail. Les enfants courent près des plots. Lila est à l'écart. Elle est près du mur. Ses épaules sont basses. Un enfant a ri un tout petit moment, puis il est parti. Pauline se souvient. On peut rejoindre. Rejoindre, c'est aller vers elle. Pauline marche vers Lila. Elle dit : tu veux jouer ? Inviter, c'est demander. Lila hésite. Pauline attend. Lila dit : d'accord. Elles marchent vers les cerceaux. Les cerceaux sont rouges. Plus tard, à la bibliothèque, Lila est encore à l'écart près des coussins. Ça continue un peu. Pauline va vers la maîtresse. La maîtresse est l'adulte. Pauline dit : ça continue. On prévient un adulte si ça continue. La maîtresse s'approche. Elle reste près d'elles. Pauline et Lila ouvrent un livre. Les pages sentent le papier. Le soir, Pauline raconte à maman. Maman dit : tu as su rejoindre. Tu as su inviter. Tu as prévenu un adulte.</t>
+          <t>Pauline est dans la cour. Maman l'a accompagnée jusqu'au portail. Les enfants courent près des plots. Lila est à l'écart. Elle est près du mur. Ses épaules sont basses. Un enfant a ri un tout petit moment, puis il est parti. Pauline se souvient. On peut rejoindre. Rejoindre, c'est aller vers elle. Pauline marche vers Lila. Tu veux jouer ? Inviter, c'est demander. Lila hésite. Pauline attend. D'accord. Elles marchent vers les cerceaux. Les cerceaux sont rouges. Plus tard, à la bibliothèque, Lila est encore à l'écart près des coussins. Ça continue un peu. Pauline va vers la maîtresse. La maîtresse est l'adulte. Ça continue. On prévient un adulte si ça continue. La maîtresse s'approche. Elle reste près d'elles. Pauline et Lila ouvrent un livre. Les pages sentent le papier. Le soir, Pauline raconte à maman. Tu as su rejoindre. Tu as su inviter. Tu as prévenu un adulte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,18 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Pauline est dans la cour. Maman l'a accompagnée jusqu'au portail. Les enfants courent près des plots. Lila est à l'écart. Elle est près du mur. Ses épaules sont basses. Un enfant a ri un tout petit moment, puis il est parti. Pauline se souvient. On peut rejoindre. Rejoindre, c'est aller vers elle. Pauline marche vers Lila.
+narrateur|Tu veux jouer ? Inviter, c'est demander.
+narrateur|Lila hésite. Pauline attend.
+copine|D'accord.
+narrateur|Elles marchent vers les cerceaux. Les cerceaux sont rouges. Plus tard, à la bibliothèque, Lila est encore à l'écart près des coussins. Ça continue un peu. Pauline va vers la maîtresse. La maîtresse est l'adulte.
+enfant-f|Ça continue. On prévient un adulte si ça continue.
+narrateur|La maîtresse s'approche. Elle reste près d'elles. Pauline et Lila ouvrent un livre. Les pages sentent le papier. Le soir, Pauline raconte à maman.
+maman|Tu as su rejoindre. Tu as su inviter. Tu as prévenu un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1493,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Lila est à l'écart. Que fait Pauline ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1666,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Pauline a su rejoindre Lila. Elle a pu inviter. Elle a prévenu un adulte, car ça continue. Maman a écouté.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1829,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Pauline range son cartable. Maman l'attend près du portail.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1996,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2036,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.002-04.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.002-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1317,6 +1322,7 @@
 maman|Tu as su rejoindre. Tu as su inviter. Tu as prévenu un adulte.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1500,6 +1506,7 @@
           <t>narrateur|Lila est à l'écart. Que fait Pauline ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1671,6 +1678,7 @@
           <t>narrateur|Pauline a su rejoindre Lila. Elle a pu inviter. Elle a prévenu un adulte, car ça continue. Maman a écouté.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1834,6 +1842,7 @@
           <t>narrateur|Pauline range son cartable. Maman l'attend près du portail.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2001,6 +2010,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2019,7 +2029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2043,6 +2053,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2244,6 +2268,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.MOQ.002-04.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.002-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pauline rejoint Lila à l'école</t>
+          <t>Victorina rejoint Nina à l'école</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>REL.MOQ.003</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le givre pique le portail. Victorina voit Nina près du mur. Elle la rejoint, l'invite aux cerceaux. À la bibliothèque, ça continue. Elle prévient la maîtresse. Le soir, elle raconte à maman.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Pauline est dans la cour. Maman l'a accompagnée jusqu'au portail. Les enfants courent près des plots. Lila est à l'écart. Elle est près du mur. Ses épaules sont basses. Un enfant a ri un tout petit moment, puis il est parti. Pauline se souvient. On peut rejoindre. Rejoindre, c'est aller vers elle. Pauline marche vers Lila. Tu veux jouer ? Inviter, c'est demander. Lila hésite. Pauline attend. D'accord. Elles marchent vers les cerceaux. Les cerceaux sont rouges. Plus tard, à la bibliothèque, Lila est encore à l'écart près des coussins. Ça continue un peu. Pauline va vers la maîtresse. La maîtresse est l'adulte. Ça continue. On prévient un adulte si ça continue. La maîtresse s'approche. Elle reste près d'elles. Pauline et Lila ouvrent un livre. Les pages sentent le papier. Le soir, Pauline raconte à maman. Tu as su rejoindre. Tu as su inviter. Tu as prévenu un adulte.</t>
+          <t>Du givre blanc pique le fer du portail. Il craque un peu, sous le doigt. L'écharpe de maman gratte, toute douce. Elle sent la laine et le savon. Des cerceaux rouges sont empilés, comme une tour. Un moineau sautille sur le mur. Tes gants sont chauds, Victorina ? Un peu. Le portail pique. C'est le givre. Il fond déjà, tu vois ? Une goutte glisse sur le fer. Je t'accompagne jusqu'ici. Tu vas jouer dans la cour ? Oui, maman. Je reviens, à la sortie. En ce moment, Victorina est dans la cour. Le sol sonne, un peu dur. Les cerceaux rouges brillent au soleil bas. Nina est à l'écart. Elle est près du mur. Ses épaules sont basses. Elle tient un cerceau, sans le faire rouler. Un enfant a ri un tout petit moment, puis il est parti. Victorina se souvient. On peut rejoindre. Rejoindre, c'est aller vers elle. Victorina marche vers Nina. Ses gants frottent, tout doux. Tu veux jouer ? Inviter, c'est demander. Nina hésite. Victorina attend. Nina dit d'accord. Elles marchent vers les cerceaux. Les cerceaux sont rouges, lisses, un peu froids. Ils roulent. Ils font un bruit rond. Je te vois encore, du portail. Maman part, tout doucement. Plus tard, c'est la bibliothèque. Ça sent le papier et le bois. Des coussins sont empilés, tout mous. Nina est encore à l'écart, près des coussins. Ça continue un peu. Victorina va vers la maîtresse. La maîtresse est l'adulte, près des livres. Ça continue. On prévient un adulte, si ça continue. Je t'écoute, Victorina. Je m'approche. La maîtresse reste près d'elles. Victorina et Nina ouvrent un livre. Les pages sentent le papier. Elles sont un peu rêche, un peu douces. Bravo. Tu as rejoint Nina. Tu l'as invitée. Tu as prévenu un adulte. On lit ensemble. Oui. La page tourne tout doux. Le soir, Victorina raconte à maman. L'écharpe est sur le crochet, maintenant. Nina était à l'écart. Je l'ai rejointe. Je l'ai invitée. Ça continuait. J'ai prévenu un adulte. Tu as su rejoindre. Tu as su inviter. Tu as prévenu un adulte. Bravo, Victorina. Tu as fait du bon travail. Tu as fini de poser tes gants ? Oui, maman. Le givre a disparu, sur le portail.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,17 +1329,89 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Pauline est dans la cour. Maman l'a accompagnée jusqu'au portail. Les enfants courent près des plots. Lila est à l'écart. Elle est près du mur. Ses épaules sont basses. Un enfant a ri un tout petit moment, puis il est parti. Pauline se souvient. On peut rejoindre. Rejoindre, c'est aller vers elle. Pauline marche vers Lila.
-narrateur|Tu veux jouer ? Inviter, c'est demander.
-narrateur|Lila hésite. Pauline attend.
-copine|D'accord.
-narrateur|Elles marchent vers les cerceaux. Les cerceaux sont rouges. Plus tard, à la bibliothèque, Lila est encore à l'écart près des coussins. Ça continue un peu. Pauline va vers la maîtresse. La maîtresse est l'adulte.
-enfant-f|Ça continue. On prévient un adulte si ça continue.
-narrateur|La maîtresse s'approche. Elle reste près d'elles. Pauline et Lila ouvrent un livre. Les pages sentent le papier. Le soir, Pauline raconte à maman.
-maman|Tu as su rejoindre. Tu as su inviter. Tu as prévenu un adulte.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Du givre blanc pique le fer du portail.
+narrateur|Il craque un peu, sous le doigt.
+narrateur|L'écharpe de maman gratte, toute douce.
+narrateur|Elle sent la laine et le savon.
+narrateur|Des cerceaux rouges sont empilés, comme une tour.
+narrateur|Un moineau sautille sur le mur.
+maman|Tes gants sont chauds, Victorina ?
+enfant-f|Un peu.
+enfant-f|Le portail pique.
+maman|C'est le givre.
+maman|Il fond déjà, tu vois ?
+narrateur|Une goutte glisse sur le fer.
+maman|Je t'accompagne jusqu'ici.
+maman|Tu vas jouer dans la cour ?
+enfant-f|Oui, maman.
+maman|Je reviens, à la sortie.
+narrateur|En ce moment, Victorina est dans la cour.
+narrateur|Le sol sonne, un peu dur.
+narrateur|Les cerceaux rouges brillent au soleil bas.
+narrateur|Nina est à l'écart.
+narrateur|Elle est près du mur.
+narrateur|Ses épaules sont basses.
+narrateur|Elle tient un cerceau, sans le faire rouler.
+narrateur|Un enfant a ri un tout petit moment, puis il est parti.
+narrateur|Victorina se souvient.
+narrateur|On peut rejoindre.
+narrateur|Rejoindre, c'est aller vers elle.
+narrateur|Victorina marche vers Nina.
+narrateur|Ses gants frottent, tout doux.
+enfant-f|Tu veux jouer ?
+narrateur|Inviter, c'est demander.
+narrateur|Nina hésite.
+narrateur|Victorina attend.
+narrateur|Nina dit d'accord.
+narrateur|Elles marchent vers les cerceaux.
+narrateur|Les cerceaux sont rouges, lisses, un peu froids.
+narrateur|Ils roulent. Ils font un bruit rond.
+maman|Je te vois encore, du portail.
+narrateur|Maman part, tout doucement.
+narrateur|Plus tard, c'est la bibliothèque.
+narrateur|Ça sent le papier et le bois.
+narrateur|Des coussins sont empilés, tout mous.
+narrateur|Nina est encore à l'écart, près des coussins.
+narrateur|Ça continue un peu.
+narrateur|Victorina va vers la maîtresse.
+narrateur|La maîtresse est l'adulte, près des livres.
+enfant-f|Ça continue.
+enfant-f|On prévient un adulte, si ça continue.
+maitresse|Je t'écoute, Victorina.
+maitresse|Je m'approche.
+narrateur|La maîtresse reste près d'elles.
+narrateur|Victorina et Nina ouvrent un livre.
+narrateur|Les pages sentent le papier.
+narrateur|Elles sont un peu rêche, un peu douces.
+maitresse|Bravo.
+maitresse|Tu as rejoint Nina.
+maitresse|Tu l'as invitée.
+maitresse|Tu as prévenu un adulte.
+enfant-f|On lit ensemble.
+maitresse|Oui.
+maitresse|La page tourne tout doux.
+narrateur|Le soir, Victorina raconte à maman.
+narrateur|L'écharpe est sur le crochet, maintenant.
+enfant-f|Nina était à l'écart.
+enfant-f|Je l'ai rejointe.
+enfant-f|Je l'ai invitée.
+enfant-f|Ça continuait.
+enfant-f|J'ai prévenu un adulte.
+maman|Tu as su rejoindre.
+maman|Tu as su inviter.
+maman|Tu as prévenu un adulte.
+maman|Bravo, Victorina.
+maman|Tu as fait du bon travail.
+maman|Tu as fini de poser tes gants ?
+enfant-f|Oui, maman.
+narrateur|Le givre a disparu, sur le portail.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1347,7 +1436,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Lila est à l'écart. Que fait Pauline ?</t>
+          <t>Nina est à l'écart. Que fait Victorina ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1503,7 +1592,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Lila est à l'écart. Que fait Pauline ?</t>
+          <t>narrateur|Nina est à l'écart.
+narrateur|Que fait Victorina ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1531,7 +1621,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Pauline a su rejoindre Lila. Elle a pu inviter. Elle a prévenu un adulte, car ça continue. Maman a écouté.</t>
+          <t>Victorina a su rejoindre Nina. Elle a pu inviter. Elle a prévenu un adulte, car ça continue. Je t'ai écoutée. Bravo. C'est du bon travail. J'ai rejoint. J'ai invité. Oui. Et un adulte, si ça continue.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1675,7 +1765,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Pauline a su rejoindre Lila. Elle a pu inviter. Elle a prévenu un adulte, car ça continue. Maman a écouté.</t>
+          <t>narrateur|Victorina a su rejoindre Nina.
+narrateur|Elle a pu inviter.
+narrateur|Elle a prévenu un adulte, car ça continue.
+maman|Je t'ai écoutée.
+maman|Bravo.
+maman|C'est du bon travail.
+enfant-f|J'ai rejoint.
+enfant-f|J'ai invité.
+maman|Oui.
+maman|Et un adulte, si ça continue.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1703,7 +1802,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Pauline range son cartable. Maman l'attend près du portail.</t>
+          <t>Victorina range son cartable. Il est lourd, ce soir ? Un peu. Le livre sent encore le papier. On l'a ouvert, avec Nina. Tu l'as invitée, près des coussins. Oui. Maman l'attend près du portail. Le fer n'est plus froid.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1839,7 +1938,15 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Pauline range son cartable. Maman l'attend près du portail.</t>
+          <t>narrateur|Victorina range son cartable.
+maman|Il est lourd, ce soir ?
+enfant-f|Un peu.
+maman|Le livre sent encore le papier.
+enfant-f|On l'a ouvert, avec Nina.
+maman|Tu l'as invitée, près des coussins.
+enfant-f|Oui.
+narrateur|Maman l'attend près du portail.
+narrateur|Le fer n'est plus froid.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1867,7 +1974,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai rejoint Nina. J'ai raconté à maman. Bravo. Tu as fait du bon travail. L'écharpe sent encore la laine. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2007,7 +2114,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai rejoint Nina.
+enfant-f|J'ai raconté à maman.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|L'écharpe sent encore la laine.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2029,7 +2141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2067,6 +2179,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.002-04.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.002-04.xlsx
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Du givre blanc pique le fer du portail. Il craque un peu, sous le doigt. L'écharpe de maman gratte, toute douce. Elle sent la laine et le savon. Des cerceaux rouges sont empilés, comme une tour. Un moineau sautille sur le mur. Tes gants sont chauds, Victorina ? Un peu. Le portail pique. C'est le givre. Il fond déjà, tu vois ? Une goutte glisse sur le fer. Je t'accompagne jusqu'ici. Tu vas jouer dans la cour ? Oui, maman. Je reviens, à la sortie. En ce moment, Victorina est dans la cour. Le sol sonne, un peu dur. Les cerceaux rouges brillent au soleil bas. Nina est à l'écart. Elle est près du mur. Ses épaules sont basses. Elle tient un cerceau, sans le faire rouler. Un enfant a ri un tout petit moment, puis il est parti. Victorina se souvient. On peut rejoindre. Rejoindre, c'est aller vers elle. Victorina marche vers Nina. Ses gants frottent, tout doux. Tu veux jouer ? Inviter, c'est demander. Nina hésite. Victorina attend. Nina dit d'accord. Elles marchent vers les cerceaux. Les cerceaux sont rouges, lisses, un peu froids. Ils roulent. Ils font un bruit rond. Je te vois encore, du portail. Maman part, tout doucement. Plus tard, c'est la bibliothèque. Ça sent le papier et le bois. Des coussins sont empilés, tout mous. Nina est encore à l'écart, près des coussins. Ça continue un peu. Victorina va vers la maîtresse. La maîtresse est l'adulte, près des livres. Ça continue. On prévient un adulte, si ça continue. Je t'écoute, Victorina. Je m'approche. La maîtresse reste près d'elles. Victorina et Nina ouvrent un livre. Les pages sentent le papier. Elles sont un peu rêche, un peu douces. Bravo. Tu as rejoint Nina. Tu l'as invitée. Tu as prévenu un adulte. On lit ensemble. Oui. La page tourne tout doux. Le soir, Victorina raconte à maman. L'écharpe est sur le crochet, maintenant. Nina était à l'écart. Je l'ai rejointe. Je l'ai invitée. Ça continuait. J'ai prévenu un adulte. Tu as su rejoindre. Tu as su inviter. Tu as prévenu un adulte. Bravo, Victorina. Tu as fait du bon travail. Tu as fini de poser tes gants ? Oui, maman. Le givre a disparu, sur le portail.</t>
+          <t>Du givre blanc pique le fer du portail. Il craque un peu, sous le doigt. L'écharpe de maman gratte, toute douce. Elle sent la laine et le savon. Des cerceaux rouges sont empilés, comme une tour. Un moineau sautille sur le mur. Tes gants sont chauds, Victorina ? Un peu. Le portail pique. C'est le givre. Il fond déjà, tu vois ? Une goutte glisse sur le fer. Je t'accompagne jusqu'ici. Tu vas jouer dans la cour ? Oui, maman. Je reviens, à la sortie. En ce moment, Victorina est dans la cour. Le sol sonne, un peu dur. Les cerceaux rouges brillent au soleil bas. Nina est à l'écart. Elle est près du mur. Ses épaules sont basses. Elle tient un cerceau, sans le faire rouler. Un enfant a ri un tout petit moment, puis il est parti. Victorina se souvient. On peut rejoindre. Rejoindre, c'est aller vers elle. Victorina marche vers Nina. Ses gants frottent, tout doux. Tu veux jouer ? Inviter, c'est demander. Nina hésite. Victorina attend. Nina dit d'accord. Elles marchent vers les cerceaux. Les cerceaux sont rouges, lisses, un peu froids. Ils roulent. Ils font un bruit rond. Je te vois encore, du portail. Maman part, tout doucement. Plus tard, c'est la bibliothèque. Ça sent le papier et le bois. Des coussins sont empilés, tout mous. Nina est encore à l'écart, près des coussins. Ça continue un peu. Victorina va vers la maîtresse. La maîtresse est l'adulte, près des livres. Ça continue. On prévient un adulte, si ça continue. Je t'écoute, Victorina. Je m'approche. La maîtresse reste près d'elles. Victorina et Nina ouvrent un livre. Les pages sentent le papier. Elles sont un peu rêche, un peu douces. Bravo. Tu as rejoint Nina. Tu l'as invitée. Tu as prévenu un adulte. On lit ensemble. Oui. La page tourne tout doux. Le soir, Victorina raconte à maman. L'écharpe est sur le crochet, maintenant. Nina était à l'écart. Je l'ai rejointe. Je l'ai invitée. Ça continuait. J'ai prévenu un adulte. Tu as su rejoindre. Tu as su inviter. Tu as prévenu un adulte. Bravo, Victorina. Tu as fini de poser tes gants ? Oui, maman. Le givre a disparu, sur le portail.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Pauline est dans la cour. Maman l'a accompagnée jusqu'au portail. Les enfants courent près des plots. Lila est à l'écart. Elle est près du mur. Ses épaules sont basses. Un enfant a ri un tout petit moment, puis il est parti. Pauline se souvient. On peut &lt;emphasis level="moderate"&gt;rejoindre&lt;/emphasis&gt;. Rejoindre, c'est aller vers elle. Pauline marche vers Lila. Elle dit : tu veux jouer ? Inviter, c'est demander. Lila hésite. Pauline attend. Lila dit : d'accord. Elles marchent vers les cerceaux. Les cerceaux sont rouges. Plus tard, à la bibliothèque, Lila est encore à l'écart près des coussins. Ça continue un peu. Pauline va vers la maîtresse. La maîtresse est l'adulte. Pauline dit : ça continue. On prévient un adulte si ça continue. La maîtresse s'approche. Elle reste près d'elles. Pauline et Lila ouvrent un livre. Les pages sentent le papier. Le soir, Pauline raconte à maman. Maman dit : tu as su rejoindre. Tu as su inviter. Tu as prévenu un adulte.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Du givre blanc pique le fer du portail. Il craque un peu, sous le doigt. L'écharpe de maman gratte, toute douce. Elle sent la laine et le savon. Des cerceaux rouges sont empilés, comme une tour. Un moineau sautille sur le mur. Tes gants sont chauds, Victorina ? Un peu. Le portail pique. C'est le givre. Il fond déjà, tu vois ? Une goutte glisse sur le fer. Je t'accompagne jusqu'ici. Tu vas jouer dans la cour ? Oui, maman. Je reviens, à la sortie. En ce moment, Victorina est dans la cour. Le sol sonne, un peu dur. Les cerceaux rouges brillent au soleil bas. Nina est à l'écart. Elle est près du mur. Ses épaules sont basses. Elle tient un cerceau, sans le faire rouler. Un enfant a ri un tout petit moment, puis il est parti. Victorina se souvient. On peut rejoindre. Rejoindre, c'est aller vers elle. Victorina marche vers Nina. Ses gants frottent, tout doux. Tu veux jouer ? Inviter, c'est demander. Nina hésite. Victorina attend. Nina dit d'accord. Elles marchent vers les cerceaux. Les cerceaux sont rouges, lisses, un peu froids. Ils roulent. Ils font un bruit rond. Je te vois encore, du portail. Maman part, tout doucement. Plus tard, c'est la bibliothèque. Ça sent le papier et le bois. Des coussins sont empilés, tout mous. Nina est encore à l'écart, près des coussins. Ça continue un peu. Victorina va vers la maîtresse. La maîtresse est l'adulte, près des livres. Ça continue. On prévient un adulte, si ça continue. Je t'écoute, Victorina. Je m'approche. La maîtresse reste près d'elles. Victorina et Nina ouvrent un livre. Les pages sentent le papier. Elles sont un peu rêche, un peu douces. Bravo. Tu as rejoint Nina. Tu l'as invitée. Tu as prévenu un adulte. On lit ensemble. Oui. La page tourne tout doux. Le soir, Victorina raconte à maman. L'écharpe est sur le crochet, maintenant. Nina était à l'écart. Je l'ai rejointe. Je l'ai invitée. Ça continuait. J'ai prévenu un adulte. Tu as su rejoindre. Tu as su inviter. Tu as prévenu un adulte. Bravo, Victorina. Tu as fini de poser tes gants ? Oui, maman. Le givre a disparu, sur le portail.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1401,7 +1401,6 @@
 maman|Tu as su inviter.
 maman|Tu as prévenu un adulte.
 maman|Bravo, Victorina.
-maman|Tu as fait du bon travail.
 maman|Tu as fini de poser tes gants ?
 enfant-f|Oui, maman.
 narrateur|Le givre a disparu, sur le portail.</t>
@@ -1441,7 +1440,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Lila est à l'écart. Que fait Pauline ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina est à l'écart. Que fait Victorina ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1596,7 +1595,6 @@
 narrateur|Que fait Victorina ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1621,12 +1619,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Victorina a su rejoindre Nina. Elle a pu inviter. Elle a prévenu un adulte, car ça continue. Je t'ai écoutée. Bravo. C'est du bon travail. J'ai rejoint. J'ai invité. Oui. Et un adulte, si ça continue.</t>
+          <t>Victorina a su rejoindre Nina. Elle a pu inviter. Elle a prévenu un adulte, car ça continue. Je t'ai écoutée. Bravo. J'ai rejoint. J'ai invité. Oui. Et un adulte, si ça continue.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Pauline a su &lt;emphasis level="moderate"&gt;rejoindre&lt;/emphasis&gt; Lila. Elle a pu inviter. Elle a prévenu un adulte, car ça continue. Maman a écouté.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina a su rejoindre Nina. Elle a pu inviter. Elle a prévenu un adulte, car ça continue. Je t'ai écoutée. Bravo. J'ai rejoint. J'ai invité. Oui. Et un adulte, si ça continue.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1770,14 +1768,12 @@
 narrateur|Elle a prévenu un adulte, car ça continue.
 maman|Je t'ai écoutée.
 maman|Bravo.
-maman|C'est du bon travail.
 enfant-f|J'ai rejoint.
 enfant-f|J'ai invité.
 maman|Oui.
 maman|Et un adulte, si ça continue.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1807,7 +1803,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Pauline range son cartable. Maman l'attend près du portail.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina range son cartable. Il est lourd, ce soir ? Un peu. Le livre sent encore le papier. On l'a ouvert, avec Nina. Tu l'as invitée, près des coussins. Oui. Maman l'attend près du portail. Le fer n'est plus froid.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1949,7 +1945,6 @@
 narrateur|Le fer n'est plus froid.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1974,12 +1969,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai rejoint Nina. J'ai raconté à maman. Bravo. Tu as fait du bon travail. L'écharpe sent encore la laine. L'histoire est finie.</t>
+          <t>J'ai rejoint Nina. J'ai raconté à maman. Bravo. L'écharpe sent encore la laine.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai rejoint Nina. J'ai raconté à maman. Bravo. L'écharpe sent encore la laine.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2117,12 +2112,9 @@
           <t>enfant-f|J'ai rejoint Nina.
 enfant-f|J'ai raconté à maman.
 maman|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|L'écharpe sent encore la laine.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|L'écharpe sent encore la laine.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2141,7 +2133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2186,6 +2178,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.002-04.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.002-04.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cour de l'école</t>
+          <t>cour de l'école puis bibliothèque</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pauline, Lila, maman, la maîtresse</t>
+          <t>Victorina, Nina, maman, maîtresse</t>
         </is>
       </c>
     </row>
